--- a/data/trending_integrated_20261028_09.xlsx
+++ b/data/trending_integrated_20261028_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>182800</v>
+        <v>182900</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+4.88%</t>
+          <t>'+4.93%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.06</v>
       </c>
       <c r="E2" t="n">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="F2" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="G2" t="n">
-        <v>795</v>
+        <v>817</v>
       </c>
       <c r="H2" t="n">
         <v>35.43</v>
@@ -610,7 +610,7 @@
         <v>35.49</v>
       </c>
       <c r="O2" t="n">
-        <v>27070512700</v>
+        <v>30773100150</v>
       </c>
       <c r="P2" t="n">
         <v>304000</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>229000</v>
+        <v>230750</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+3.15%</t>
+          <t>'+3.94%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="F3" t="n">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="G3" t="n">
-        <v>2395</v>
+        <v>2444</v>
       </c>
       <c r="H3" t="n">
         <v>46.15</v>
@@ -702,7 +702,7 @@
         <v>46.1</v>
       </c>
       <c r="O3" t="n">
-        <v>236618283000</v>
+        <v>299327495000</v>
       </c>
       <c r="P3" t="n">
         <v>374500</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1366000</v>
+        <v>1368000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.86%</t>
+          <t>'+2.01%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="G4" t="n">
-        <v>1706</v>
+        <v>1576</v>
       </c>
       <c r="H4" t="n">
         <v>48.61</v>
@@ -794,7 +794,7 @@
         <v>48.66</v>
       </c>
       <c r="O4" t="n">
-        <v>525540449500</v>
+        <v>634922172000</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>실적 및 주주환원 정책에 대한 긍정적 언급과 함께 자사주 매입 계획이 제시되었으나, 순이익 감소에 대한 우려와 일부 매도 의견도 존재한다.</t>
+          <t>SK하이닉스, 2030년까지 수요 우위 전망 및 20조 규모 자사주 매입 시작 예정. 실적 호조와 주주환원 정책 기대감 속 외인 매수세 유입.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['실적', '주주환원', '자사주 매입']</t>
+          <t>['주주환원', '자사주매입', '수요 전망']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="H5" t="n">
         <v>10.31</v>
@@ -886,7 +886,7 @@
         <v>10.34</v>
       </c>
       <c r="O5" t="n">
-        <v>10818553350</v>
+        <v>12549610600</v>
       </c>
       <c r="P5" t="n">
         <v>154800</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>증권사 목표가 하향 조정과 공매도 관련 언급이 다수 나타나며, 실적 부진에 대한 우려로 주가 하락 전망이 우세하다.</t>
+          <t>한화오션, 2분기 실적 호조에도 주가 하락세 지속. 공매도 및 부정적 증권사 리포트 영향으로 하락 압력 발생. 4분기 실적 전망 불투명.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['공매도', '목표가 하향', '실적 부진']</t>
+          <t>['실적', '공매도', '증권사 리포트']</t>
         </is>
       </c>
       <c r="X5" t="n">

--- a/data/trending_integrated_20261028_09.xlsx
+++ b/data/trending_integrated_20261028_09.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>182900</v>
+        <v>234500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+4.93%</t>
+          <t>'+5.63%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>245</v>
+        <v>542</v>
       </c>
       <c r="F2" t="n">
-        <v>172</v>
+        <v>303</v>
       </c>
       <c r="G2" t="n">
-        <v>817</v>
+        <v>2544</v>
       </c>
       <c r="H2" t="n">
-        <v>35.43</v>
+        <v>46.15</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,38 +595,38 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>174300</v>
+        <v>222000</v>
       </c>
       <c r="K2" t="n">
-        <v>181100</v>
+        <v>231000</v>
       </c>
       <c r="L2" t="n">
-        <v>184600</v>
+        <v>234500</v>
       </c>
       <c r="M2" t="n">
-        <v>180000</v>
+        <v>228000</v>
       </c>
       <c r="N2" t="n">
-        <v>35.49</v>
+        <v>46.1</v>
       </c>
       <c r="O2" t="n">
-        <v>30773100150</v>
+        <v>502560959250</v>
       </c>
       <c r="P2" t="n">
-        <v>304000</v>
+        <v>374500</v>
       </c>
       <c r="Q2" t="n">
-        <v>170900</v>
+        <v>94500</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>79000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 증시 강세와 브룩필드 투자 확정 소식에 대한 기대감이 있으나, 기관 및 외인 매도세와 윗꼬리 달리는 흐름에 대한 불안감도 공존한다.</t>
+          <t>미국 증시 반도체 관련주 강세와 모건스탠리의 목표가 상향 조정에 따른 기대감이 반영되었으나, 일부 부정적인 정치적 언급이 혼재되어 있다.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,11 +635,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['브룩필드 투자', '기관 외인 매도', '프로그램 매수']</t>
+          <t>['반도체', '바닥 확인', '목표가 상향']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>035420</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>230750</v>
+        <v>183500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+3.94%</t>
+          <t>'+5.28%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="E3" t="n">
-        <v>481</v>
+        <v>269</v>
       </c>
       <c r="F3" t="n">
-        <v>275</v>
+        <v>181</v>
       </c>
       <c r="G3" t="n">
-        <v>2444</v>
+        <v>882</v>
       </c>
       <c r="H3" t="n">
-        <v>46.15</v>
+        <v>35.43</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>222000</v>
+        <v>174300</v>
       </c>
       <c r="K3" t="n">
-        <v>231000</v>
+        <v>181100</v>
       </c>
       <c r="L3" t="n">
-        <v>231500</v>
+        <v>184600</v>
       </c>
       <c r="M3" t="n">
-        <v>228000</v>
+        <v>180000</v>
       </c>
       <c r="N3" t="n">
-        <v>46.1</v>
+        <v>35.49</v>
       </c>
       <c r="O3" t="n">
-        <v>299327495000</v>
+        <v>38160236900</v>
       </c>
       <c r="P3" t="n">
-        <v>374500</v>
+        <v>304000</v>
       </c>
       <c r="Q3" t="n">
-        <v>94500</v>
+        <v>170900</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-40000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 증시 반도체 관련주 강세와 모건스탠리의 목표가 상향 조정에 따른 기대감이 반영되었으나, 일부 부정적인 정치적 언급이 혼재되어 있다.</t>
+          <t>NAVER, 브룩필드 투자 확정 및 기관, 외인 쌍매도. 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '바닥 확인', '목표가 상향']</t>
+          <t>['브룩필드 투자', '프로그램 매수', '쌍매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>035420</t>
         </is>
       </c>
     </row>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1368000</v>
+        <v>1393500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.01%</t>
+          <t>'+3.91%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G4" t="n">
-        <v>1576</v>
+        <v>1510</v>
       </c>
       <c r="H4" t="n">
         <v>48.61</v>
@@ -785,7 +785,7 @@
         <v>1390000</v>
       </c>
       <c r="L4" t="n">
-        <v>1390000</v>
+        <v>1394000</v>
       </c>
       <c r="M4" t="n">
         <v>1358000</v>
@@ -794,7 +794,7 @@
         <v>48.66</v>
       </c>
       <c r="O4" t="n">
-        <v>634922172000</v>
+        <v>819472127500</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -803,23 +803,23 @@
         <v>501000</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-19000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>SK하이닉스, 2030년까지 수요 우위 전망 및 20조 규모 자사주 매입 시작 예정. 실적 호조와 주주환원 정책 기대감 속 외인 매수세 유입.</t>
+          <t>SK하이닉스, 자사주 매입 및 주주환원 정책 발표. 2030년까지 수요 우위 지속 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주주환원', '자사주매입', '수요 전망']</t>
+          <t>['자사주 매입', '주주환원', '수요 전망']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52400</v>
+        <v>52000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.13%</t>
+          <t>'-1.89%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="G5" t="n">
-        <v>204</v>
+        <v>273</v>
       </c>
       <c r="H5" t="n">
         <v>10.31</v>
@@ -886,7 +886,7 @@
         <v>10.34</v>
       </c>
       <c r="O5" t="n">
-        <v>12549610600</v>
+        <v>18656253800</v>
       </c>
       <c r="P5" t="n">
         <v>154800</v>
@@ -895,23 +895,23 @@
         <v>51200</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-138000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>한화오션, 2분기 실적 호조에도 주가 하락세 지속. 공매도 및 부정적 증권사 리포트 영향으로 하락 압력 발생. 4분기 실적 전망 불투명.</t>
+          <t>한화오션, 실적 부진 및 악재 뉴스 지속. 공매도 세력의 하향 기사 쏟아짐.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '증권사 리포트']</t>
+          <t>['실적 부진', '공매도', '악재 뉴스']</t>
         </is>
       </c>
       <c r="X5" t="n">

--- a/data/trending_integrated_20261028_09.xlsx
+++ b/data/trending_integrated_20261028_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>234500</v>
+        <v>3730</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+5.63%</t>
+          <t>'+15.48%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>542</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>303</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>2544</v>
+        <v>81</v>
       </c>
       <c r="H2" t="n">
-        <v>46.15</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>222000</v>
+        <v>3230</v>
       </c>
       <c r="K2" t="n">
-        <v>231000</v>
+        <v>3600</v>
       </c>
       <c r="L2" t="n">
-        <v>234500</v>
+        <v>3990</v>
       </c>
       <c r="M2" t="n">
-        <v>228000</v>
+        <v>3580</v>
       </c>
       <c r="N2" t="n">
-        <v>46.1</v>
+        <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>502560959250</v>
+        <v>55845100765</v>
       </c>
       <c r="P2" t="n">
-        <v>374500</v>
+        <v>8100</v>
       </c>
       <c r="Q2" t="n">
-        <v>94500</v>
+        <v>592</v>
       </c>
       <c r="R2" t="n">
-        <v>79000</v>
+        <v>97000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 증시 반도체 관련주 강세와 모건스탠리의 목표가 상향 조정에 따른 기대감이 반영되었으나, 일부 부정적인 정치적 언급이 혼재되어 있다.</t>
+          <t>미국 광통신주 급등에 따른 기대감 형성. 갭 상승 후 변동성 나타내며 단기 차익 실현 매물 출현.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['반도체', '바닥 확인', '목표가 상향']</t>
+          <t>['광통신', '갭 상승', '변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>183500</v>
+        <v>186100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+5.28%</t>
+          <t>'+6.77%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.06</v>
       </c>
       <c r="E3" t="n">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="F3" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G3" t="n">
-        <v>882</v>
+        <v>919</v>
       </c>
       <c r="H3" t="n">
         <v>35.43</v>
@@ -693,7 +693,7 @@
         <v>181100</v>
       </c>
       <c r="L3" t="n">
-        <v>184600</v>
+        <v>186900</v>
       </c>
       <c r="M3" t="n">
         <v>180000</v>
@@ -702,7 +702,7 @@
         <v>35.49</v>
       </c>
       <c r="O3" t="n">
-        <v>38160236900</v>
+        <v>49511557550</v>
       </c>
       <c r="P3" t="n">
         <v>304000</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>NAVER, 브룩필드 투자 확정 및 기관, 외인 쌍매도. 프로그램 매수세 관찰.</t>
+          <t>엔비디아의 3대 주주 등극 및 브룩필드 투자 확정 소식. 야간 선물 급등 및 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['브룩필드 투자', '프로그램 매수', '쌍매도']</t>
+          <t>['엔비디아', '브룩필드', '투자 확정']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1393500</v>
+        <v>233750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.91%</t>
+          <t>'+5.29%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>609</v>
       </c>
       <c r="F4" t="n">
-        <v>517</v>
+        <v>331</v>
       </c>
       <c r="G4" t="n">
-        <v>1510</v>
+        <v>2671</v>
       </c>
       <c r="H4" t="n">
-        <v>48.61</v>
+        <v>46.15</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1341000</v>
+        <v>222000</v>
       </c>
       <c r="K4" t="n">
-        <v>1390000</v>
+        <v>231000</v>
       </c>
       <c r="L4" t="n">
-        <v>1394000</v>
+        <v>235000</v>
       </c>
       <c r="M4" t="n">
-        <v>1358000</v>
+        <v>228000</v>
       </c>
       <c r="N4" t="n">
-        <v>48.66</v>
+        <v>46.1</v>
       </c>
       <c r="O4" t="n">
-        <v>819472127500</v>
+        <v>594213123000</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q4" t="n">
-        <v>501000</v>
+        <v>94500</v>
       </c>
       <c r="R4" t="n">
-        <v>-19000</v>
+        <v>79000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>SK하이닉스, 자사주 매입 및 주주환원 정책 발표. 2030년까지 수요 우위 지속 전망.</t>
+          <t>미국 증시 반도체 관련주 강세와 모건스탠리의 목표가 상향 조정에 따른 기대감이 반영되었으나, 일부 부정적인 정치적 언급이 혼재되어 있다.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['자사주 매입', '주주환원', '수요 전망']</t>
+          <t>['반도체', '바닥 확인', '목표가 상향']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52000</v>
+        <v>14350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.89%</t>
+          <t>'+4.74%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>273</v>
+        <v>72</v>
       </c>
       <c r="H5" t="n">
-        <v>10.31</v>
+        <v>2.87</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>53000</v>
+        <v>13700</v>
       </c>
       <c r="K5" t="n">
-        <v>53400</v>
+        <v>14210</v>
       </c>
       <c r="L5" t="n">
-        <v>53800</v>
+        <v>14800</v>
       </c>
       <c r="M5" t="n">
-        <v>51200</v>
+        <v>14210</v>
       </c>
       <c r="N5" t="n">
-        <v>10.34</v>
+        <v>2.82</v>
       </c>
       <c r="O5" t="n">
-        <v>18656253800</v>
+        <v>44490334750</v>
       </c>
       <c r="P5" t="n">
-        <v>154800</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>51200</v>
+        <v>1760</v>
       </c>
       <c r="R5" t="n">
-        <v>-138000</v>
+        <v>295000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>한화오션, 실적 부진 및 악재 뉴스 지속. 공매도 세력의 하향 기사 쏟아짐.</t>
+          <t>미국 광통신주 급등 및 외인 프로그램 매수세 유입. 3분기 실적 발표 후 변동성 예상.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,18 +911,386 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적 부진', '공매도', '악재 뉴스']</t>
+          <t>['광통신', '외인 매수', '실적 발표']</t>
         </is>
       </c>
       <c r="X5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1377000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'+2.68%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E6" t="n">
+        <v>800</v>
+      </c>
+      <c r="F6" t="n">
+        <v>506</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1533</v>
+      </c>
+      <c r="H6" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1341000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1390000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1396000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1358000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>48.66</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1028784677000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>501000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-19000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>내년부터 100조 주주 환원 발표 및 2030년까지 수요 우위 지속 전망. 20조 규모 자사주 매입 시작 예정.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['주주 환원', '자사주 매입', '수요 전망']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>63500</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'+2.09%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E7" t="n">
+        <v>42</v>
+      </c>
+      <c r="F7" t="n">
+        <v>32</v>
+      </c>
+      <c r="G7" t="n">
+        <v>200</v>
+      </c>
+      <c r="H7" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>62200</v>
+      </c>
+      <c r="K7" t="n">
+        <v>63000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>63900</v>
+      </c>
+      <c r="M7" t="n">
+        <v>62200</v>
+      </c>
+      <c r="N7" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="O7" t="n">
+        <v>60007325450</v>
+      </c>
+      <c r="P7" t="n">
+        <v>67300</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>23150</v>
+      </c>
+      <c r="R7" t="n">
+        <v>83000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>중동 전쟁 종전 기대감에 따른 국제유가 하락과 더불어 최근 4일간 코스피 수익률 1위 달성. 자사주 매입 및 향후 전망 긍정적.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['추세 전환', '자사주 매입', '전망']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>14410</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-0.28%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="E8" t="n">
+        <v>48</v>
+      </c>
+      <c r="F8" t="n">
+        <v>32</v>
+      </c>
+      <c r="G8" t="n">
+        <v>91</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>14450</v>
+      </c>
+      <c r="K8" t="n">
+        <v>14750</v>
+      </c>
+      <c r="L8" t="n">
+        <v>14870</v>
+      </c>
+      <c r="M8" t="n">
+        <v>14310</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="O8" t="n">
+        <v>12236883585</v>
+      </c>
+      <c r="P8" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-147000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>주가 조작 및 공매도 의혹 제기. 부정적 의견 및 불만 표출.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['주가 조작', '공매도', '주주 원성']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>한화오션</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>51900</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-2.08%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E9" t="n">
+        <v>120</v>
+      </c>
+      <c r="F9" t="n">
+        <v>93</v>
+      </c>
+      <c r="G9" t="n">
+        <v>377</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>53000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>53400</v>
+      </c>
+      <c r="L9" t="n">
+        <v>53800</v>
+      </c>
+      <c r="M9" t="n">
+        <v>51200</v>
+      </c>
+      <c r="N9" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="O9" t="n">
+        <v>24526620700</v>
+      </c>
+      <c r="P9" t="n">
+        <v>154800</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>51200</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-138000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2분기 실적 하회 및 4분기 실적 부진 전망. 공매도 및 부정적 기사 쏟아지는 가운데 주가 하락.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['실적 부진', '공매도', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
         <v>1</v>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>042660</t>
         </is>

--- a/data/trending_integrated_20261028_09.xlsx
+++ b/data/trending_integrated_20261028_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3730</v>
+        <v>3720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+15.48%</t>
+          <t>'+15.17%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>55845100765</v>
+        <v>60833869016</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감 형성. 갭 상승 후 변동성 나타내며 단기 차익 실현 매물 출현.</t>
+          <t>빛과전자, 미국 광통신주 강세에 따른 상승 기대감. 갭 상승 후 변동성 확대, 단기 차익 매물 출회.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '갭 상승', '변동성']</t>
+          <t>['광통신', '갭상승', '변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>186100</v>
+        <v>186000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.77%</t>
+          <t>'+6.71%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.06</v>
       </c>
       <c r="E3" t="n">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="F3" t="n">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="G3" t="n">
-        <v>919</v>
+        <v>1012</v>
       </c>
       <c r="H3" t="n">
         <v>35.43</v>
@@ -702,7 +702,7 @@
         <v>35.49</v>
       </c>
       <c r="O3" t="n">
-        <v>49511557550</v>
+        <v>56432758000</v>
       </c>
       <c r="P3" t="n">
         <v>304000</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>엔비디아의 3대 주주 등극 및 브룩필드 투자 확정 소식. 야간 선물 급등 및 긍정적 흐름 기대.</t>
+          <t>NAVER, 엔비디아 투자 확정 및 코어위브 강세 속 상승 기대. 기관, 외인 쌍매도 속 28층 보유자 불안감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['엔비디아', '브룩필드', '투자 확정']</t>
+          <t>['엔비디아', '기관매도', '프로그램']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>233750</v>
+        <v>234500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.29%</t>
+          <t>'+5.63%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>609</v>
+        <v>658</v>
       </c>
       <c r="F4" t="n">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="G4" t="n">
-        <v>2671</v>
+        <v>2816</v>
       </c>
       <c r="H4" t="n">
         <v>46.15</v>
@@ -785,7 +785,7 @@
         <v>231000</v>
       </c>
       <c r="L4" t="n">
-        <v>235000</v>
+        <v>235500</v>
       </c>
       <c r="M4" t="n">
         <v>228000</v>
@@ -794,7 +794,7 @@
         <v>46.1</v>
       </c>
       <c r="O4" t="n">
-        <v>594213123000</v>
+        <v>749329852750</v>
       </c>
       <c r="P4" t="n">
         <v>374500</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14350</v>
+        <v>14360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.74%</t>
+          <t>'+4.82%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="H5" t="n">
         <v>2.87</v>
@@ -886,7 +886,7 @@
         <v>2.82</v>
       </c>
       <c r="O5" t="n">
-        <v>44490334750</v>
+        <v>47277546195</v>
       </c>
       <c r="P5" t="n">
         <v>31500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등 및 외인 프로그램 매수세 유입. 3분기 실적 발표 후 변동성 예상.</t>
+          <t>대한광통신, 미국 광통신주 급등에 따른 수혜 기대. 외인 프로그램 매수세 유입 확인, 실적 발표 예정.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '외인 매수', '실적 발표']</t>
+          <t>['광통신', '외인매수', '실적']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1377000</v>
+        <v>30600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.68%</t>
+          <t>'+3.73%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>506</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>1533</v>
+        <v>170</v>
       </c>
       <c r="H6" t="n">
-        <v>48.61</v>
+        <v>28.81</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1341000</v>
+        <v>29500</v>
       </c>
       <c r="K6" t="n">
-        <v>1390000</v>
+        <v>29900</v>
       </c>
       <c r="L6" t="n">
-        <v>1396000</v>
+        <v>30650</v>
       </c>
       <c r="M6" t="n">
-        <v>1358000</v>
+        <v>29900</v>
       </c>
       <c r="N6" t="n">
-        <v>48.66</v>
+        <v>28.82</v>
       </c>
       <c r="O6" t="n">
-        <v>1028784677000</v>
+        <v>13120478925</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>69700</v>
       </c>
       <c r="Q6" t="n">
-        <v>501000</v>
+        <v>29200</v>
       </c>
       <c r="R6" t="n">
-        <v>-19000</v>
+        <v>94000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>내년부터 100조 주주 환원 발표 및 2030년까지 수요 우위 지속 전망. 20조 규모 자사주 매입 시작 예정.</t>
+          <t>카카오, 지속적인 하락 추세 속에서 공매도에 대한 불만 제기. 주가 반등 기대감 있으나 불확실.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주주 환원', '자사주 매입', '수요 전망']</t>
+          <t>['하락', '공매도', '적정주가']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>035720</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63500</v>
+        <v>1387000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.09%</t>
+          <t>'+3.43%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.57</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>497</v>
       </c>
       <c r="G7" t="n">
-        <v>200</v>
+        <v>1490</v>
       </c>
       <c r="H7" t="n">
-        <v>41.01</v>
+        <v>48.61</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>62200</v>
+        <v>1341000</v>
       </c>
       <c r="K7" t="n">
-        <v>63000</v>
+        <v>1390000</v>
       </c>
       <c r="L7" t="n">
-        <v>63900</v>
+        <v>1396000</v>
       </c>
       <c r="M7" t="n">
-        <v>62200</v>
+        <v>1358000</v>
       </c>
       <c r="N7" t="n">
-        <v>40.44</v>
+        <v>48.66</v>
       </c>
       <c r="O7" t="n">
-        <v>60007325450</v>
+        <v>1190380140000</v>
       </c>
       <c r="P7" t="n">
-        <v>67300</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>23150</v>
+        <v>501000</v>
       </c>
       <c r="R7" t="n">
-        <v>83000</v>
+        <v>-19000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>중동 전쟁 종전 기대감에 따른 국제유가 하락과 더불어 최근 4일간 코스피 수익률 1위 달성. 자사주 매입 및 향후 전망 긍정적.</t>
+          <t>SK하이닉스, 2030년까지 수요 우위 지속 전망. 대규모 주주환원 정책 발표 및 자사주 매입 시작.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['추세 전환', '자사주 매입', '전망']</t>
+          <t>['주주환원', '자사주매입', '수요']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14410</v>
+        <v>63400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.28%</t>
+          <t>'+1.93%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.19</v>
+        <v>0.57</v>
       </c>
       <c r="E8" t="n">
         <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>91</v>
+        <v>227</v>
       </c>
       <c r="H8" t="n">
-        <v>9.83</v>
+        <v>41.01</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14450</v>
+        <v>62200</v>
       </c>
       <c r="K8" t="n">
-        <v>14750</v>
+        <v>63000</v>
       </c>
       <c r="L8" t="n">
-        <v>14870</v>
+        <v>63900</v>
       </c>
       <c r="M8" t="n">
-        <v>14310</v>
+        <v>62200</v>
       </c>
       <c r="N8" t="n">
-        <v>10.02</v>
+        <v>40.44</v>
       </c>
       <c r="O8" t="n">
-        <v>12236883585</v>
+        <v>66877010000</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R8" t="n">
-        <v>-147000</v>
+        <v>83000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도 의혹 제기. 부정적 의견 및 불만 표출.</t>
+          <t>삼성E&amp;A, 최근 수익률 1위 달성. 중동 전쟁 종식 기대감 및 자사주 매입 지속, 추세 전환 유력.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '주주 원성']</t>
+          <t>['자사주매입', '전쟁종식', '수익률']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51900</v>
+        <v>14380</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.08%</t>
+          <t>'-0.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.03</v>
+        <v>-0.19</v>
       </c>
       <c r="E9" t="n">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>377</v>
+        <v>129</v>
       </c>
       <c r="H9" t="n">
-        <v>10.31</v>
+        <v>9.83</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,244 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>53000</v>
+        <v>14450</v>
       </c>
       <c r="K9" t="n">
-        <v>53400</v>
+        <v>14750</v>
       </c>
       <c r="L9" t="n">
-        <v>53800</v>
+        <v>14870</v>
       </c>
       <c r="M9" t="n">
-        <v>51200</v>
+        <v>14310</v>
       </c>
       <c r="N9" t="n">
-        <v>10.34</v>
+        <v>10.02</v>
       </c>
       <c r="O9" t="n">
-        <v>24526620700</v>
+        <v>15394705345</v>
       </c>
       <c r="P9" t="n">
-        <v>154800</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>51200</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-138000</v>
+        <v>-147000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2분기 실적 하회 및 4분기 실적 부진 전망. 공매도 및 부정적 기사 쏟아지는 가운데 주가 하락.</t>
+          <t>대우건설, 주가 하락 및 공매도 공세에 대한 불만 고조. 중동 전쟁 종식 기대감이 있으나 주가 부진.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['공매', '주가조작', '연기금']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>한화오션</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>52400</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-1.13%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E10" t="n">
+        <v>146</v>
+      </c>
+      <c r="F10" t="n">
+        <v>113</v>
+      </c>
+      <c r="G10" t="n">
+        <v>453</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>53000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>53400</v>
+      </c>
+      <c r="L10" t="n">
+        <v>53800</v>
+      </c>
+      <c r="M10" t="n">
+        <v>51200</v>
+      </c>
+      <c r="N10" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="O10" t="n">
+        <v>28334903200</v>
+      </c>
+      <c r="P10" t="n">
+        <v>154800</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>51200</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-138000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>한화오션, 2분기 실적 부진 및 4분기 전망 불확실성. 외국인 폭탄 매도 속 주가 급락.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
         <v>0.1</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>['실적 부진', '공매도', '주가 하락']</t>
-        </is>
-      </c>
-      <c r="X9" t="n">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['실적', '공매도', '악재']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
         <v>1</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>042660</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SK증권</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1985</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-4.80%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E11" t="n">
+        <v>43</v>
+      </c>
+      <c r="F11" t="n">
+        <v>33</v>
+      </c>
+      <c r="G11" t="n">
+        <v>42</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2085</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2005</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2010</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1805</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O11" t="n">
+        <v>9511362747</v>
+      </c>
+      <c r="P11" t="n">
+        <v>6190</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>636</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-393000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SK증권, 지수 상승에도 하락하며 원인 불분명. 매각이 최우선 과제라는 의견 대립.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['액면병합', '공매도', '매각']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>001510</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261028_09.xlsx
+++ b/data/trending_integrated_20261028_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3720</v>
+        <v>3695</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+15.17%</t>
+          <t>'+14.40%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>60833869016</v>
+        <v>64294378876</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>빛과전자, 미국 광통신주 강세에 따른 상승 기대감. 갭 상승 후 변동성 확대, 단기 차익 매물 출회.</t>
+          <t>빛과전자, 미국 광통신주 강세 영향. 단기 급등 후 변동성 확대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '갭상승', '변동성']</t>
+          <t>['광통신', '호재', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>186000</v>
+        <v>187300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.71%</t>
+          <t>'+9.47%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
-        <v>198</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>1012</v>
+        <v>119</v>
       </c>
       <c r="H3" t="n">
-        <v>35.43</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>174300</v>
+        <v>171100</v>
       </c>
       <c r="K3" t="n">
-        <v>181100</v>
+        <v>176300</v>
       </c>
       <c r="L3" t="n">
-        <v>186900</v>
+        <v>187400</v>
       </c>
       <c r="M3" t="n">
-        <v>180000</v>
+        <v>175400</v>
       </c>
       <c r="N3" t="n">
-        <v>35.49</v>
+        <v>74.89</v>
       </c>
       <c r="O3" t="n">
-        <v>56432758000</v>
+        <v>286339260500</v>
       </c>
       <c r="P3" t="n">
-        <v>304000</v>
+        <v>243500</v>
       </c>
       <c r="Q3" t="n">
-        <v>170900</v>
+        <v>71000</v>
       </c>
       <c r="R3" t="n">
-        <v>-40000</v>
+        <v>187000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-22000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>NAVER, 엔비디아 투자 확정 및 코어위브 강세 속 상승 기대. 기관, 외인 쌍매도 속 28층 보유자 불안감.</t>
+          <t>삼성전자우, 외국인 매수세 유입되며 급등. 숏 스퀴즈 및 소각 기대감 반영.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['엔비디아', '기관매도', '프로그램']</t>
+          <t>['우선주', '소각', '외국인']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>035420</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>234500</v>
+        <v>185100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.63%</t>
+          <t>'+6.20%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>321</v>
       </c>
       <c r="F4" t="n">
-        <v>349</v>
+        <v>205</v>
       </c>
       <c r="G4" t="n">
-        <v>2816</v>
+        <v>1063</v>
       </c>
       <c r="H4" t="n">
-        <v>46.15</v>
+        <v>35.43</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>222000</v>
+        <v>174300</v>
       </c>
       <c r="K4" t="n">
-        <v>231000</v>
+        <v>181100</v>
       </c>
       <c r="L4" t="n">
-        <v>235500</v>
+        <v>186900</v>
       </c>
       <c r="M4" t="n">
-        <v>228000</v>
+        <v>180000</v>
       </c>
       <c r="N4" t="n">
-        <v>46.1</v>
+        <v>35.49</v>
       </c>
       <c r="O4" t="n">
-        <v>749329852750</v>
+        <v>61809663050</v>
       </c>
       <c r="P4" t="n">
-        <v>374500</v>
+        <v>304000</v>
       </c>
       <c r="Q4" t="n">
-        <v>94500</v>
+        <v>170900</v>
       </c>
       <c r="R4" t="n">
-        <v>79000</v>
+        <v>-40000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 증시 반도체 관련주 강세와 모건스탠리의 목표가 상향 조정에 따른 기대감이 반영되었으나, 일부 부정적인 정치적 언급이 혼재되어 있다.</t>
+          <t>NAVER, 엔비디아 투자 확정 및 코어위브 강세 속 상승 기대. 기관, 외인 쌍매도 속 28층 보유자 불안감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '바닥 확인', '목표가 상향']</t>
+          <t>['엔비디아', '기관매도', '프로그램']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>035420</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14360</v>
+        <v>235750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.82%</t>
+          <t>'+6.19%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>708</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>376</v>
       </c>
       <c r="G5" t="n">
-        <v>108</v>
+        <v>2968</v>
       </c>
       <c r="H5" t="n">
-        <v>2.87</v>
+        <v>46.15</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13700</v>
+        <v>222000</v>
       </c>
       <c r="K5" t="n">
-        <v>14210</v>
+        <v>231000</v>
       </c>
       <c r="L5" t="n">
-        <v>14800</v>
+        <v>236000</v>
       </c>
       <c r="M5" t="n">
-        <v>14210</v>
+        <v>228000</v>
       </c>
       <c r="N5" t="n">
-        <v>2.82</v>
+        <v>46.1</v>
       </c>
       <c r="O5" t="n">
-        <v>47277546195</v>
+        <v>819924206500</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>1760</v>
+        <v>94500</v>
       </c>
       <c r="R5" t="n">
-        <v>295000</v>
+        <v>79000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>339000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대한광통신, 미국 광통신주 급등에 따른 수혜 기대. 외인 프로그램 매수세 유입 확인, 실적 발표 예정.</t>
+          <t>미국 증시 반도체 관련주 강세와 모건스탠리의 목표가 상향 조정에 따른 기대감이 반영되었으나, 일부 부정적인 정치적 언급이 혼재되어 있다.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '외인매수', '실적']</t>
+          <t>['반도체', '바닥 확인', '목표가 상향']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30600</v>
+        <v>14420</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.73%</t>
+          <t>'+5.26%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="H6" t="n">
-        <v>28.81</v>
+        <v>2.87</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>29500</v>
+        <v>13700</v>
       </c>
       <c r="K6" t="n">
-        <v>29900</v>
+        <v>14210</v>
       </c>
       <c r="L6" t="n">
-        <v>30650</v>
+        <v>14800</v>
       </c>
       <c r="M6" t="n">
-        <v>29900</v>
+        <v>14210</v>
       </c>
       <c r="N6" t="n">
-        <v>28.82</v>
+        <v>2.82</v>
       </c>
       <c r="O6" t="n">
-        <v>13120478925</v>
+        <v>48808056555</v>
       </c>
       <c r="P6" t="n">
-        <v>69700</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>29200</v>
+        <v>1760</v>
       </c>
       <c r="R6" t="n">
-        <v>94000</v>
+        <v>295000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>카카오, 지속적인 하락 추세 속에서 공매도에 대한 불만 제기. 주가 반등 기대감 있으나 불확실.</t>
+          <t>대한광통신, 외국인 및 프로그램 매수 유입. 광통신 섹터 강세 영향.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['하락', '공매도', '적정주가']</t>
+          <t>['광통신', '외인', '매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1387000</v>
+        <v>1400000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.43%</t>
+          <t>'+4.40%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G7" t="n">
-        <v>1490</v>
+        <v>1485</v>
       </c>
       <c r="H7" t="n">
         <v>48.61</v>
@@ -1061,7 +1061,7 @@
         <v>1390000</v>
       </c>
       <c r="L7" t="n">
-        <v>1396000</v>
+        <v>1400000</v>
       </c>
       <c r="M7" t="n">
         <v>1358000</v>
@@ -1070,7 +1070,7 @@
         <v>48.66</v>
       </c>
       <c r="O7" t="n">
-        <v>1190380140000</v>
+        <v>1360186135000</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1082,11 +1082,11 @@
         <v>-19000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>SK하이닉스, 2030년까지 수요 우위 지속 전망. 대규모 주주환원 정책 발표 및 자사주 매입 시작.</t>
+          <t>SK하이닉스, 100조 주주 환원 계획 발표. 자사주 매입 및 배당 기대감으로 상승.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주주환원', '자사주매입', '수요']</t>
+          <t>['주주환원', '자사주매입', '실적']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63400</v>
+        <v>30500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.93%</t>
+          <t>'+3.39%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.57</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>227</v>
+        <v>170</v>
       </c>
       <c r="H8" t="n">
-        <v>41.01</v>
+        <v>28.81</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>62200</v>
+        <v>29500</v>
       </c>
       <c r="K8" t="n">
-        <v>63000</v>
+        <v>29900</v>
       </c>
       <c r="L8" t="n">
-        <v>63900</v>
+        <v>30650</v>
       </c>
       <c r="M8" t="n">
-        <v>62200</v>
+        <v>29900</v>
       </c>
       <c r="N8" t="n">
-        <v>40.44</v>
+        <v>28.82</v>
       </c>
       <c r="O8" t="n">
-        <v>66877010000</v>
+        <v>14941431025</v>
       </c>
       <c r="P8" t="n">
-        <v>67300</v>
+        <v>69700</v>
       </c>
       <c r="Q8" t="n">
-        <v>23150</v>
+        <v>29200</v>
       </c>
       <c r="R8" t="n">
-        <v>83000</v>
+        <v>94000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 최근 수익률 1위 달성. 중동 전쟁 종식 기대감 및 자사주 매입 지속, 추세 전환 유력.</t>
+          <t>카카오, 하락세 지속. 추가 상장 우려 및 부진한 주가 흐름.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주매입', '전쟁종식', '수익률']</t>
+          <t>['하락', '적정주가', '공매']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>035720</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14380</v>
+        <v>63900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.48%</t>
+          <t>'+2.73%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.19</v>
+        <v>0.57</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>129</v>
+        <v>243</v>
       </c>
       <c r="H9" t="n">
-        <v>9.83</v>
+        <v>41.01</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14450</v>
+        <v>62200</v>
       </c>
       <c r="K9" t="n">
-        <v>14750</v>
+        <v>63000</v>
       </c>
       <c r="L9" t="n">
-        <v>14870</v>
+        <v>63900</v>
       </c>
       <c r="M9" t="n">
-        <v>14310</v>
+        <v>62200</v>
       </c>
       <c r="N9" t="n">
-        <v>10.02</v>
+        <v>40.44</v>
       </c>
       <c r="O9" t="n">
-        <v>15394705345</v>
+        <v>76310808700</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R9" t="n">
-        <v>-147000</v>
+        <v>83000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>대우건설, 주가 하락 및 공매도 공세에 대한 불만 고조. 중동 전쟁 종식 기대감이 있으나 주가 부진.</t>
+          <t>삼성E&amp;A, 최근 코스피 수익률 1위 기록. 평화 회담 기대감 및 자사주 매입 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공매', '주가조작', '연기금']</t>
+          <t>['추세', '전망', '자사주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52400</v>
+        <v>14400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.13%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.03</v>
+        <v>-0.19</v>
       </c>
       <c r="E10" t="n">
-        <v>146</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
-        <v>113</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>453</v>
+        <v>142</v>
       </c>
       <c r="H10" t="n">
-        <v>10.31</v>
+        <v>9.83</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>53000</v>
+        <v>14450</v>
       </c>
       <c r="K10" t="n">
-        <v>53400</v>
+        <v>14750</v>
       </c>
       <c r="L10" t="n">
-        <v>53800</v>
+        <v>14870</v>
       </c>
       <c r="M10" t="n">
-        <v>51200</v>
+        <v>14310</v>
       </c>
       <c r="N10" t="n">
-        <v>10.34</v>
+        <v>10.02</v>
       </c>
       <c r="O10" t="n">
-        <v>28334903200</v>
+        <v>17328362825</v>
       </c>
       <c r="P10" t="n">
-        <v>154800</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>51200</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-138000</v>
+        <v>-147000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-31000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>한화오션, 2분기 실적 부진 및 4분기 전망 불확실성. 외국인 폭탄 매도 속 주가 급락.</t>
+          <t>대우건설, 주주 불만 고조. 공매도 및 매도 압력 지속. 명확한 호재 없이 부진.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '악재']</t>
+          <t>['공매', '주주', '매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>042660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1985</v>
+        <v>52400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.80%</t>
+          <t>'-1.13%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.39</v>
+        <v>-0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>43</v>
+        <v>158</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="G11" t="n">
-        <v>42</v>
+        <v>491</v>
       </c>
       <c r="H11" t="n">
-        <v>2.52</v>
+        <v>10.31</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2085</v>
+        <v>53000</v>
       </c>
       <c r="K11" t="n">
-        <v>2005</v>
+        <v>53400</v>
       </c>
       <c r="L11" t="n">
-        <v>2010</v>
+        <v>53800</v>
       </c>
       <c r="M11" t="n">
-        <v>1805</v>
+        <v>51200</v>
       </c>
       <c r="N11" t="n">
-        <v>2.13</v>
+        <v>10.34</v>
       </c>
       <c r="O11" t="n">
-        <v>9511362747</v>
+        <v>31289125700</v>
       </c>
       <c r="P11" t="n">
-        <v>6190</v>
+        <v>154800</v>
       </c>
       <c r="Q11" t="n">
-        <v>636</v>
+        <v>51200</v>
       </c>
       <c r="R11" t="n">
-        <v>-393000</v>
+        <v>-138000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-22000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>SK증권, 지수 상승에도 하락하며 원인 불분명. 매각이 최우선 과제라는 의견 대립.</t>
+          <t>한화오션, 매출 증가에도 주가 하락. 외국인 및 프로그램 매도세 지속.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['액면병합', '공매도', '매각']</t>
+          <t>['매출', '외인', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1475,6 +1475,98 @@
         </is>
       </c>
       <c r="Z11" t="inlineStr">
+        <is>
+          <t>042660</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SK증권</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1984</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-4.84%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E12" t="n">
+        <v>47</v>
+      </c>
+      <c r="F12" t="n">
+        <v>36</v>
+      </c>
+      <c r="G12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2085</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2005</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2010</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1805</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O12" t="n">
+        <v>9816255002</v>
+      </c>
+      <c r="P12" t="n">
+        <v>6190</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>636</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-393000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>SK증권, 지수 대비 하락세 지속. 개인 매도 추정. 명확한 호재 부재.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['분석', '전망', '매각']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>001510</t>
         </is>
